--- a/TFM_mao/resultados/technical_batch/anova_drug.xlsx
+++ b/TFM_mao/resultados/technical_batch/anova_drug.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>P_adj</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Veredicto</t>
         </is>
       </c>
@@ -462,7 +467,10 @@
       <c r="C2" t="n">
         <v>2.09294525576435e-18</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>2.41493683357425e-18</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -480,7 +488,10 @@
       <c r="C3" t="n">
         <v>1.995050455936509e-78</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>5.985151367809528e-78</v>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -498,7 +509,10 @@
       <c r="C4" t="n">
         <v>3.12745092308783e-183</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="n">
+        <v>4.691176384631745e-182</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -516,7 +530,10 @@
       <c r="C5" t="n">
         <v>2.453770595541466e-121</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="n">
+        <v>1.840327946656099e-120</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -534,7 +551,10 @@
       <c r="C6" t="n">
         <v>1.345601226964349e-32</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="n">
+        <v>1.682001533705436e-32</v>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -552,7 +572,10 @@
       <c r="C7" t="n">
         <v>1.216113816127506e-116</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" t="n">
+        <v>7.296682896765035e-116</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -570,7 +593,10 @@
       <c r="C8" t="n">
         <v>2.834205894017466e-64</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" t="n">
+        <v>7.085514735043665e-64</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -588,7 +614,10 @@
       <c r="C9" t="n">
         <v>5.033112461776071e-85</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" t="n">
+        <v>1.677704153925357e-84</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -606,7 +635,10 @@
       <c r="C10" t="n">
         <v>2.015185016262142e-133</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" t="n">
+        <v>2.015185016262142e-132</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -624,7 +656,10 @@
       <c r="C11" t="n">
         <v>1.144690447152619e-111</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" t="n">
+        <v>5.723452235763093e-111</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -642,7 +677,10 @@
       <c r="C12" t="n">
         <v>1.166372993683509e-50</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" t="n">
+        <v>2.058305282970899e-50</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -660,7 +698,10 @@
       <c r="C13" t="n">
         <v>1.355211904934804e-58</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" t="n">
+        <v>2.904025510574579e-58</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -678,7 +719,10 @@
       <c r="C14" t="n">
         <v>2.60540550909517e-73</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" t="n">
+        <v>7.105651388441373e-73</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -696,7 +740,10 @@
       <c r="C15" t="n">
         <v>2.363152252868317e-187</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" t="n">
+        <v>7.089456758604952e-186</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -714,7 +761,10 @@
       <c r="C16" t="n">
         <v>5.926302121429168e-56</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" t="n">
+        <v>1.111181647767969e-55</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -732,7 +782,10 @@
       <c r="C17" t="n">
         <v>4.331875579236168e-43</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" t="n">
+        <v>6.497813368854251e-43</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -750,7 +803,10 @@
       <c r="C18" t="n">
         <v>2.773579997085884e-92</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" t="n">
+        <v>1.040092498907207e-91</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -768,7 +824,10 @@
       <c r="C19" t="n">
         <v>8.551616977838264e-43</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" t="n">
+        <v>1.221659568262609e-42</v>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -786,7 +845,10 @@
       <c r="C20" t="n">
         <v>1.594247090284517e-42</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" t="n">
+        <v>2.173973304933433e-42</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -804,7 +866,10 @@
       <c r="C21" t="n">
         <v>6.365686522346364e-47</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" t="n">
+        <v>1.005108398265215e-46</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -822,7 +887,10 @@
       <c r="C22" t="n">
         <v>5.325530000143125e-39</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" t="n">
+        <v>6.946343478447554e-39</v>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -840,7 +908,10 @@
       <c r="C23" t="n">
         <v>2.185779503550219e-24</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" t="n">
+        <v>2.622935404260263e-24</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -858,7 +929,10 @@
       <c r="C24" t="n">
         <v>3.68758413947679e-08</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" t="n">
+        <v>3.950983006582275e-08</v>
+      </c>
+      <c r="E24" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -876,7 +950,10 @@
       <c r="C25" t="n">
         <v>1.140515823231101e-58</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" t="n">
+        <v>2.631959592071771e-58</v>
+      </c>
+      <c r="E25" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -894,7 +971,10 @@
       <c r="C26" t="n">
         <v>9.048708946741056e-57</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" t="n">
+        <v>1.809741789348211e-56</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -912,7 +992,10 @@
       <c r="C27" t="n">
         <v>0.0005202107360491204</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" t="n">
+        <v>0.0005381490372921936</v>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -930,7 +1013,10 @@
       <c r="C28" t="n">
         <v>1.627614060635679e-95</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" t="n">
+        <v>6.975488831295765e-95</v>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -948,7 +1034,10 @@
       <c r="C29" t="n">
         <v>2.367570249309855e-12</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" t="n">
+        <v>2.630633610344284e-12</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -966,7 +1055,10 @@
       <c r="C30" t="n">
         <v>1.165085516011534e-49</v>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" t="n">
+        <v>1.941809193352556e-49</v>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>Significativo</t>
         </is>
@@ -984,7 +1076,10 @@
       <c r="C31" t="n">
         <v>0.9999999999863105</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" t="n">
+        <v>0.9999999999863105</v>
+      </c>
+      <c r="E31" t="inlineStr">
         <is>
           <t>No significativo</t>
         </is>
